--- a/outputs/base-maestra-egm-20261024/Base_Maestra_EGM_Actualizada_2026-10-24.xlsx
+++ b/outputs/base-maestra-egm-20261024/Base_Maestra_EGM_Actualizada_2026-10-24.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" r:id="R6057023b28504808"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instalaciones" sheetId="2" r:id="R61bbe947949c4f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upgrades_Plataforma" sheetId="3" r:id="Rdf6275d521b14921"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_General" sheetId="4" r:id="Rbb90ba6dc2b648f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="5" r:id="R780b0c6219a441fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen_Modelos" sheetId="6" r:id="R9b480d3f4f534a6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hotelera_Detalle" sheetId="7" r:id="R8d0e1d7d596546da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" r:id="Rf0fbd157016a497c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instalaciones" sheetId="2" r:id="R64dd3ab695a1413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upgrades_Plataforma" sheetId="3" r:id="R54eb8ce03c1b4af4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_General" sheetId="4" r:id="R8302983d977e49b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="5" r:id="Rab8f38df33ac4879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen_Modelos" sheetId="6" r:id="R0d94411365b24a7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hotelera_Detalle" sheetId="7" r:id="R3a7196d99586497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FV837E_Detalle" sheetId="8" r:id="R339fccfac425449d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -70,6 +71,30 @@
       <x:sz val="12"/>
       <x:color rgb="FF14253F"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF14253F"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF64748B"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
       <x:scheme val="minor"/>
     </x:font>
@@ -146,7 +171,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -174,6 +199,32 @@
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -282,6 +333,24 @@
     <x:tableColumn id="5" name="Jackpot Controllers"/>
     <x:tableColumn id="6" name="Cartelería"/>
     <x:tableColumn id="7" name="Estado"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FV837EDetalle" displayName="FV837EDetalle" ref="A4:J28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="Isla"/>
+    <x:tableColumn id="2" name="Cliente / destino"/>
+    <x:tableColumn id="3" name="Modelo"/>
+    <x:tableColumn id="4" name="EGM en isla"/>
+    <x:tableColumn id="5" name="Número de serie"/>
+    <x:tableColumn id="6" name="Juego"/>
+    <x:tableColumn id="7" name="Cartelería"/>
+    <x:tableColumn id="8" name="Posiciones"/>
+    <x:tableColumn id="9" name="Estado"/>
+    <x:tableColumn id="10" name="Isla linkeada"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -588,20 +657,16 @@
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EGM asignadas a Hotelera Emprender</x:t>
-        </x:is>
+      <x:c r="A3" s="2" t="str">
+        <x:v>EGM comprometidas con Hotelera Emprender</x:v>
       </x:c>
       <x:c r="B3" s="2" t="n">
         <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EGM stock sin destino</x:t>
-        </x:is>
+      <x:c r="A4" s="2" t="str">
+        <x:v>EGM sin destino o en preparación</x:v>
       </x:c>
       <x:c r="B4" s="2" t="n">
         <x:v>32</x:v>
@@ -638,10 +703,8 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">STOCK GENERAL</x:t>
-        </x:is>
+      <x:c r="A8" s="2" t="str">
+        <x:v>STOCK GENERAL INFORMADO</x:v>
       </x:c>
       <x:c r="B8" s="2" t="n">
         <x:v>176</x:v>
@@ -1831,7 +1894,7 @@
         </x:is>
       </x:c>
       <x:c r="K2" s="2" t="str">
-        <x:v>Villa Mercedes; 1 isla linkeada, 1 Jackpot Controller; fecha de instalación TBD. Ver Hotelera_Detalle.</x:v>
+        <x:v>Contrato firmado; 1 de las 3 islas retirada por el cliente (modelo sin identificar) y 2 pendientes de retiro. Ninguna instalada ni operativa. Esta fila FV834 no está identificada como la retirada.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1880,7 +1943,7 @@
         </x:is>
       </x:c>
       <x:c r="K3" s="2" t="str">
-        <x:v>Villa Mercedes; 1 isla linkeada, 1 Jackpot Controller; 4 RENO 100935 y 4 RENO 100955. Fecha de instalación TBD. Ver Hotelera_Detalle.</x:v>
+        <x:v>Estado general de retiro: ver STK-001. Esta isla no está identificada como la retirada.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1931,7 +1994,7 @@
         </x:is>
       </x:c>
       <x:c r="K4" s="2" t="str">
-        <x:v>Villa Mercedes; 1 isla linkeada, 1 Jackpot Controller; cartelería Fazi. Fecha de instalación TBD. Ver Hotelera_Detalle.</x:v>
+        <x:v>Estado general de retiro: ver STK-001. Esta isla no está identificada como la retirada.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1990,58 +2053,36 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">STK-005</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FV837E</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EGM</x:t>
-        </x:is>
+      <x:c r="A6" s="2" t="str">
+        <x:v>STK-005</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="str">
+        <x:v>EGM</x:v>
       </x:c>
       <x:c r="D6" s="2" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Xtension Link Evolution o Superia WinWays</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fazi</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="J6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Stock / preparación</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pack Ruby; 8 en preparación y 16 stock sin destino; configuración final pendiente</x:t>
-        </x:is>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E6" s="2" t="str"/>
+      <x:c r="F6" s="2" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="G6" s="2" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="H6" s="2" t="str">
+        <x:v>Fazi · 8 posiciones</x:v>
+      </x:c>
+      <x:c r="I6" s="2" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="J6" s="2" t="str">
+        <x:v>Stock / preparación</x:v>
+      </x:c>
+      <x:c r="K6" s="2" t="str">
+        <x:v>Isla 1 de 3; 8 FV837E en preparación. Ver FV837E_Detalle para las series.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2262,6 +2303,72 @@
         <x:is>
           <x:t xml:space="preserve">Nuevo ingreso a stock</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2" t="str">
+        <x:v>STK-010</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>EGM</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="str"/>
+      <x:c r="F11" s="2" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="G11" s="2" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="H11" s="2" t="str">
+        <x:v>Fazi · 8 posiciones</x:v>
+      </x:c>
+      <x:c r="I11" s="2" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="J11" s="2" t="str">
+        <x:v>Stock / preparación</x:v>
+      </x:c>
+      <x:c r="K11" s="2" t="str">
+        <x:v>Isla 2 de 3; 8 FV837E en preparación. Ver FV837E_Detalle para las series.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2" t="str">
+        <x:v>STK-011</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="str">
+        <x:v>EGM</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="str"/>
+      <x:c r="F12" s="2" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="G12" s="2" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="H12" s="2" t="str">
+        <x:v>Fazi · 8 posiciones</x:v>
+      </x:c>
+      <x:c r="I12" s="2" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="J12" s="2" t="str">
+        <x:v>Stock / preparación</x:v>
+      </x:c>
+      <x:c r="K12" s="2" t="str">
+        <x:v>Isla 3 de 3; 8 FV837E en preparación. Ver FV837E_Detalle para las series.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2361,30 +2468,24 @@
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G2" s="2" t="inlineStr">
+      <x:c r="F2" s="2" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="str">
+        <x:v>Villa Mercedes</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TBD</x:t>
         </x:is>
       </x:c>
-      <x:c r="H2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TBD</x:t>
-        </x:is>
-      </x:c>
       <x:c r="I2" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Asignado</x:t>
         </x:is>
       </x:c>
-      <x:c r="J2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
+      <x:c r="J2" s="2" t="str">
+        <x:v>Contrato firmado; 1 de las 3 islas retirada por el cliente (modelo sin identificar) y 2 pendientes de retiro. Ninguna instalada ni operativa.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2401,40 +2502,32 @@
       <x:c r="C3" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ultra Boost o Cash Connection Edition 3</x:t>
-        </x:is>
+      <x:c r="D3" s="2" t="str">
+        <x:v>Ultraboost Tiger Storm (4) / Ultraboost Grand Eagle (4)</x:v>
       </x:c>
       <x:c r="E3" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="G3" s="2" t="inlineStr">
+      <x:c r="F3" s="2" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="str">
+        <x:v>Villa Mercedes</x:v>
+      </x:c>
+      <x:c r="H3" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TBD</x:t>
         </x:is>
       </x:c>
-      <x:c r="H3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TBD</x:t>
-        </x:is>
-      </x:c>
       <x:c r="I3" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Asignado</x:t>
         </x:is>
       </x:c>
-      <x:c r="J3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Juego pendiente de confirmar</x:t>
-        </x:is>
+      <x:c r="J3" s="2" t="str">
+        <x:v>Juego y cantidades por juego: 4 RENO 100935 Ultraboost Tiger Storm y 4 RENO 100955 Ultraboost Grand Eagle. Estado de retiro general: ver fila FV834.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2461,30 +2554,24 @@
           <x:t xml:space="preserve">Fazi</x:t>
         </x:is>
       </x:c>
-      <x:c r="F4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sí</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="2" t="inlineStr">
+      <x:c r="F4" s="2" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="G4" s="2" t="str">
+        <x:v>Villa Mercedes</x:v>
+      </x:c>
+      <x:c r="H4" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TBD</x:t>
         </x:is>
       </x:c>
-      <x:c r="H4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TBD</x:t>
-        </x:is>
-      </x:c>
       <x:c r="I4" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Asignado</x:t>
         </x:is>
       </x:c>
-      <x:c r="J4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
+      <x:c r="J4" s="2" t="str">
+        <x:v>Estado general de retiro: ver fila FV834.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2602,10 +2689,8 @@
       <x:c r="B7" s="2" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pack Ruby: 8 en preparación + 16 stock sin destino</x:t>
-        </x:is>
+      <x:c r="C7" s="2" t="str">
+        <x:v>24 en preparación: 3 islas de 8 para EPIC CASINO, GOLDEN PALACE SAN LUIS y FLAMINGO; Xtension Link Evolution; cartelería Fazi de 8 posiciones.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2707,7 +2792,7 @@
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>Ubicación Villa Mercedes indicada por el usuario; estado asignado / pendiente de instalación y fecha TBD según fuente. Tres bloques de modelo corresponden a tres islas linkeadas, cada una con 1 Jackpot Controller. El controller no se suma como EGM.</x:v>
+        <x:v>Contrato firmado. El cliente retiró 1 de las 3 islas y las otras 2 siguen en el depósito, pendientes de retiro. Falta identificar el modelo de la isla retirada. Ninguna está instalada ni operativa. Las tres islas linkeadas tienen 1 Jackpot Controller cada una; la fecha de instalación sigue TBD.</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -3976,8 +4061,860 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R728bc0617221405a"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21d63d5f727c4d8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d13d6f22dc641b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09dbe630c4084abe"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>FV837E en preparación · 24 EGM</x:v>
+      </x:c>
+      <x:c r="B1" s="25"/>
+      <x:c r="C1" s="25"/>
+      <x:c r="D1" s="25"/>
+      <x:c r="E1" s="25"/>
+      <x:c r="F1" s="25"/>
+      <x:c r="G1" s="25"/>
+      <x:c r="H1" s="25"/>
+      <x:c r="I1" s="25"/>
+      <x:c r="J1" s="25"/>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="28" t="str">
+        <x:v>Información facilitada por el usuario: 3 islas de 8, Xtension Link Evolution y cartelería Fazi de 8 posiciones. No se informó RENO ID ni Jackpot Controller para estas islas.</x:v>
+      </x:c>
+      <x:c r="B2" s="28"/>
+      <x:c r="C2" s="28"/>
+      <x:c r="D2" s="28"/>
+      <x:c r="E2" s="28"/>
+      <x:c r="F2" s="28"/>
+      <x:c r="G2" s="28"/>
+      <x:c r="H2" s="28"/>
+      <x:c r="I2" s="28"/>
+      <x:c r="J2" s="28"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="21" t="str">
+        <x:v>Isla</x:v>
+      </x:c>
+      <x:c r="B4" s="21" t="str">
+        <x:v>Cliente / destino</x:v>
+      </x:c>
+      <x:c r="C4" s="21" t="str">
+        <x:v>Modelo</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="str">
+        <x:v>EGM en isla</x:v>
+      </x:c>
+      <x:c r="E4" s="21" t="str">
+        <x:v>Número de serie</x:v>
+      </x:c>
+      <x:c r="F4" s="21" t="str">
+        <x:v>Juego</x:v>
+      </x:c>
+      <x:c r="G4" s="21" t="str">
+        <x:v>Cartelería</x:v>
+      </x:c>
+      <x:c r="H4" s="21" t="str">
+        <x:v>Posiciones</x:v>
+      </x:c>
+      <x:c r="I4" s="21" t="str">
+        <x:v>Estado</x:v>
+      </x:c>
+      <x:c r="J4" s="21" t="str">
+        <x:v>Isla linkeada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="21" t="str">
+        <x:v>1 de 3</x:v>
+      </x:c>
+      <x:c r="B5" s="21" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="C5" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D5" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E5" s="21" t="str">
+        <x:v>10110563</x:v>
+      </x:c>
+      <x:c r="F5" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G5" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H5" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I5" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J5" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="21" t="str">
+        <x:v>1 de 3</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="C6" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D6" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E6" s="21" t="str">
+        <x:v>10110564</x:v>
+      </x:c>
+      <x:c r="F6" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G6" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H6" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I6" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J6" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="21" t="str">
+        <x:v>1 de 3</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="C7" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D7" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E7" s="21" t="str">
+        <x:v>10110565</x:v>
+      </x:c>
+      <x:c r="F7" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G7" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H7" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J7" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="21" t="str">
+        <x:v>1 de 3</x:v>
+      </x:c>
+      <x:c r="B8" s="21" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="str">
+        <x:v>10110566</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H8" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="21" t="str">
+        <x:v>1 de 3</x:v>
+      </x:c>
+      <x:c r="B9" s="21" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="str">
+        <x:v>10110567</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H9" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I9" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="21" t="str">
+        <x:v>1 de 3</x:v>
+      </x:c>
+      <x:c r="B10" s="21" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D10" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E10" s="21" t="str">
+        <x:v>10110568</x:v>
+      </x:c>
+      <x:c r="F10" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G10" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H10" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I10" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J10" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="21" t="str">
+        <x:v>1 de 3</x:v>
+      </x:c>
+      <x:c r="B11" s="21" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E11" s="21" t="str">
+        <x:v>10110569</x:v>
+      </x:c>
+      <x:c r="F11" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G11" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H11" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I11" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J11" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="21" t="str">
+        <x:v>1 de 3</x:v>
+      </x:c>
+      <x:c r="B12" s="21" t="str">
+        <x:v>EPIC CASINO</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D12" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E12" s="21" t="str">
+        <x:v>10110570</x:v>
+      </x:c>
+      <x:c r="F12" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G12" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H12" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I12" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J12" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="21" t="str">
+        <x:v>2 de 3</x:v>
+      </x:c>
+      <x:c r="B13" s="21" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D13" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E13" s="21" t="str">
+        <x:v>10110571</x:v>
+      </x:c>
+      <x:c r="F13" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G13" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H13" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I13" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J13" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="21" t="str">
+        <x:v>2 de 3</x:v>
+      </x:c>
+      <x:c r="B14" s="21" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D14" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E14" s="21" t="str">
+        <x:v>10110572</x:v>
+      </x:c>
+      <x:c r="F14" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G14" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H14" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I14" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J14" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="21" t="str">
+        <x:v>2 de 3</x:v>
+      </x:c>
+      <x:c r="B15" s="21" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D15" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E15" s="21" t="str">
+        <x:v>10110573</x:v>
+      </x:c>
+      <x:c r="F15" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G15" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H15" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I15" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J15" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="21" t="str">
+        <x:v>2 de 3</x:v>
+      </x:c>
+      <x:c r="B16" s="21" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D16" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E16" s="21" t="str">
+        <x:v>10110574</x:v>
+      </x:c>
+      <x:c r="F16" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G16" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H16" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I16" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J16" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="21" t="str">
+        <x:v>2 de 3</x:v>
+      </x:c>
+      <x:c r="B17" s="21" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="C17" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D17" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E17" s="21" t="str">
+        <x:v>10110575</x:v>
+      </x:c>
+      <x:c r="F17" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G17" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H17" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I17" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J17" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="21" t="str">
+        <x:v>2 de 3</x:v>
+      </x:c>
+      <x:c r="B18" s="21" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D18" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E18" s="21" t="str">
+        <x:v>10110576</x:v>
+      </x:c>
+      <x:c r="F18" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G18" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H18" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I18" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J18" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="21" t="str">
+        <x:v>2 de 3</x:v>
+      </x:c>
+      <x:c r="B19" s="21" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="C19" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D19" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E19" s="21" t="str">
+        <x:v>10110577</x:v>
+      </x:c>
+      <x:c r="F19" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G19" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H19" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I19" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J19" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="21" t="str">
+        <x:v>2 de 3</x:v>
+      </x:c>
+      <x:c r="B20" s="21" t="str">
+        <x:v>GOLDEN PALACE SAN LUIS</x:v>
+      </x:c>
+      <x:c r="C20" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D20" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E20" s="21" t="str">
+        <x:v>10110578</x:v>
+      </x:c>
+      <x:c r="F20" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G20" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H20" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I20" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J20" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="21" t="str">
+        <x:v>3 de 3</x:v>
+      </x:c>
+      <x:c r="B21" s="21" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="C21" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D21" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E21" s="21" t="str">
+        <x:v>10110579</x:v>
+      </x:c>
+      <x:c r="F21" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G21" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H21" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I21" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J21" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="21" t="str">
+        <x:v>3 de 3</x:v>
+      </x:c>
+      <x:c r="B22" s="21" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="C22" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D22" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E22" s="21" t="str">
+        <x:v>10110580</x:v>
+      </x:c>
+      <x:c r="F22" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G22" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H22" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I22" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J22" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="21" t="str">
+        <x:v>3 de 3</x:v>
+      </x:c>
+      <x:c r="B23" s="21" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="C23" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D23" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E23" s="21" t="str">
+        <x:v>10110581</x:v>
+      </x:c>
+      <x:c r="F23" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G23" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H23" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I23" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J23" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="21" t="str">
+        <x:v>3 de 3</x:v>
+      </x:c>
+      <x:c r="B24" s="21" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="C24" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D24" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E24" s="21" t="str">
+        <x:v>10110582</x:v>
+      </x:c>
+      <x:c r="F24" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G24" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H24" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I24" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J24" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="21" t="str">
+        <x:v>3 de 3</x:v>
+      </x:c>
+      <x:c r="B25" s="21" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="C25" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D25" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E25" s="21" t="str">
+        <x:v>10110583</x:v>
+      </x:c>
+      <x:c r="F25" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G25" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H25" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I25" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J25" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="21" t="str">
+        <x:v>3 de 3</x:v>
+      </x:c>
+      <x:c r="B26" s="21" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="C26" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D26" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E26" s="21" t="str">
+        <x:v>10110584</x:v>
+      </x:c>
+      <x:c r="F26" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G26" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H26" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I26" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J26" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="21" t="str">
+        <x:v>3 de 3</x:v>
+      </x:c>
+      <x:c r="B27" s="21" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="C27" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D27" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E27" s="21" t="str">
+        <x:v>10110585</x:v>
+      </x:c>
+      <x:c r="F27" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G27" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H27" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I27" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J27" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="21" t="str">
+        <x:v>3 de 3</x:v>
+      </x:c>
+      <x:c r="B28" s="21" t="str">
+        <x:v>FLAMINGO</x:v>
+      </x:c>
+      <x:c r="C28" s="21" t="str">
+        <x:v>FV837E</x:v>
+      </x:c>
+      <x:c r="D28" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E28" s="21" t="str">
+        <x:v>10110586</x:v>
+      </x:c>
+      <x:c r="F28" s="21" t="str">
+        <x:v>Xtension Link Evolution</x:v>
+      </x:c>
+      <x:c r="G28" s="21" t="str">
+        <x:v>Fazi</x:v>
+      </x:c>
+      <x:c r="H28" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I28" s="21" t="str">
+        <x:v>En preparación</x:v>
+      </x:c>
+      <x:c r="J28" s="21" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb662e714b224cf3"/>
   </x:tableParts>
 </x:worksheet>
 </file>